--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
@@ -157,7 +157,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -167,12 +167,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -222,17 +216,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,61 +46,22 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-05-22</t>
-  </si>
-  <si>
-    <t>1156 Добрич бул. Добруджа</t>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>Добрич Добруджа</t>
   </si>
   <si>
     <t>ТХ7410АК</t>
   </si>
   <si>
-    <t>КТ1</t>
-  </si>
-  <si>
     <t>78970153027720621</t>
   </si>
   <si>
-    <t>78970153027720639</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>18:20:00</t>
-  </si>
-  <si>
-    <t>16:52:00</t>
-  </si>
-  <si>
-    <t>16:54:00</t>
-  </si>
-  <si>
-    <t>3231750900 3231750900</t>
-  </si>
-  <si>
-    <t>3232069901 3232069901</t>
-  </si>
-  <si>
-    <t>3232253759 3232253759</t>
   </si>
   <si>
     <t>Общи литри по продукт / КИРОВ ТУР ООД</t>
@@ -521,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -530,17 +488,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -574,219 +529,113 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H2">
+        <v>113.97</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="J2">
+        <v>117.51</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2">
-        <v>1.65</v>
-      </c>
-      <c r="I2" s="1">
-        <v>109.89</v>
-      </c>
-      <c r="J2">
-        <v>1.79</v>
-      </c>
-      <c r="K2" s="1">
-        <v>119.21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
+      <c r="E6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B7" s="6">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1.61</v>
+      </c>
+      <c r="E7" s="6">
+        <v>113.97</v>
+      </c>
+      <c r="F7" s="6">
+        <v>117.51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>35.37</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3">
-        <v>1.64</v>
-      </c>
-      <c r="I3" s="1">
-        <v>58.01</v>
-      </c>
-      <c r="J3">
-        <v>1.75</v>
-      </c>
-      <c r="K3" s="1">
-        <v>61.9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>77</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4">
-        <v>1.63</v>
-      </c>
-      <c r="I4" s="1">
-        <v>125.51</v>
-      </c>
-      <c r="J4">
-        <v>1.74</v>
-      </c>
-      <c r="K4" s="1">
-        <v>133.98</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="6">
-        <v>178.97</v>
-      </c>
-      <c r="C9" s="6">
-        <v>3</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.6394</v>
-      </c>
-      <c r="E9" s="6">
-        <v>293.41</v>
-      </c>
-      <c r="F9" s="6">
-        <v>315.09</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="9">
-        <v>178.97</v>
-      </c>
-      <c r="C10" s="9">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="9">
-        <v>293.41</v>
-      </c>
-      <c r="F10" s="9">
-        <v>315.09</v>
+      <c r="B8" s="9">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="9">
+        <v>113.97</v>
+      </c>
+      <c r="F8" s="9">
+        <v>117.51</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-04</t>
   </si>
   <si>
@@ -58,7 +67,10 @@
     <t>2026-06-23</t>
   </si>
   <si>
-    <t>Добрич Добруджа</t>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
   </si>
   <si>
     <t>ТХ7410АК</t>
@@ -76,16 +88,37 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-04 17:32:16</t>
-  </si>
-  <si>
-    <t>2026-06-18 07:00:42</t>
-  </si>
-  <si>
-    <t>2026-06-18 10:44:51</t>
-  </si>
-  <si>
-    <t>2026-06-23 09:25:30</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>17:32:00</t>
+  </si>
+  <si>
+    <t>07:00:00</t>
+  </si>
+  <si>
+    <t>10:44:00</t>
+  </si>
+  <si>
+    <t>09:25:00</t>
+  </si>
+  <si>
+    <t>21:06:00</t>
+  </si>
+  <si>
+    <t>3232870610 3232870610</t>
+  </si>
+  <si>
+    <t>3233536557 3233536557</t>
+  </si>
+  <si>
+    <t>3233537973 3233537973</t>
+  </si>
+  <si>
+    <t>3233772008 3233772008</t>
+  </si>
+  <si>
+    <t>3234062045 3234062045</t>
   </si>
   <si>
     <t>Общи литри по продукт / КИРОВ ТУР ООД</t>
@@ -503,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -512,14 +545,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -553,218 +589,307 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>70.79000000000001</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2">
         <v>1.58</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>111.85</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.66</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>117.51</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>40.41</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3">
         <v>1.54</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>62.23</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.58</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>63.85</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>75.33</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4">
         <v>1.54</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>116.01</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.58</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>119.02</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>39.89</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5">
         <v>1.47</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>58.64</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.52</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>60.63</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="3" t="s">
+      <c r="F6">
+        <v>36.47</v>
+      </c>
+      <c r="G6" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="6">
-        <v>226.42</v>
-      </c>
-      <c r="C10" s="6">
-        <v>4</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.5402</v>
-      </c>
-      <c r="E10" s="6">
-        <v>348.73</v>
-      </c>
-      <c r="F10" s="6">
-        <v>361.01</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="8" t="s">
+      <c r="H6">
+        <v>1.43</v>
+      </c>
+      <c r="I6" s="1">
+        <v>52.15</v>
+      </c>
+      <c r="J6">
+        <v>1.51</v>
+      </c>
+      <c r="K6" s="1">
+        <v>55.07</v>
+      </c>
+      <c r="L6" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="9">
-        <v>226.42</v>
-      </c>
-      <c r="C11" s="9">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="9">
-        <v>348.73</v>
-      </c>
-      <c r="F11" s="9">
-        <v>361.01</v>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="6">
+        <v>262.89</v>
+      </c>
+      <c r="C11" s="6">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.5249</v>
+      </c>
+      <c r="E11" s="6">
+        <v>400.88</v>
+      </c>
+      <c r="F11" s="6">
+        <v>416.08</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="9">
+        <v>262.89</v>
+      </c>
+      <c r="C12" s="9">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="9">
+        <v>400.88</v>
+      </c>
+      <c r="F12" s="9">
+        <v>416.08</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,13 +55,25 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-02</t>
   </si>
   <si>
     <t>2026-07-07</t>
   </si>
   <si>
-    <t>Добрич Добруджа</t>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
   </si>
   <si>
     <t>ТХ7410АК</t>
@@ -76,10 +91,37 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-02 16:58:52</t>
-  </si>
-  <si>
-    <t>2026-07-07 13:41:23</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>16:58:00</t>
+  </si>
+  <si>
+    <t>13:41:00</t>
+  </si>
+  <si>
+    <t>09:39:00</t>
+  </si>
+  <si>
+    <t>17:14:00</t>
+  </si>
+  <si>
+    <t>07:57:00</t>
+  </si>
+  <si>
+    <t>3234197678 3234197678</t>
+  </si>
+  <si>
+    <t>3234454022 3234454022</t>
+  </si>
+  <si>
+    <t>3235055451 3235055451</t>
+  </si>
+  <si>
+    <t>3235530391 3235530391</t>
+  </si>
+  <si>
+    <t>3235647116 3235647116</t>
   </si>
   <si>
     <t>Общи литри по продукт / КИРОВ ТУР ООД</t>
@@ -497,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -506,15 +548,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -551,154 +595,304 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>61.51</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
         <v>1.43</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>87.95999999999999</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.51</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>92.88</v>
       </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>38.82</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3">
         <v>1.44</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>55.9</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.52</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>59.01</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="L3">
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>36.33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>1.56</v>
+      </c>
+      <c r="I4" s="1">
+        <v>56.67</v>
+      </c>
+      <c r="J4">
+        <v>1.68</v>
+      </c>
+      <c r="K4" s="1">
+        <v>61.03</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3" t="s">
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="4" t="s">
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5">
+        <v>1.7</v>
+      </c>
+      <c r="I5" s="1">
+        <v>113.36</v>
+      </c>
+      <c r="J5">
+        <v>1.74</v>
+      </c>
+      <c r="K5" s="1">
+        <v>116.02</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="E6" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="F6">
+        <v>36.91</v>
+      </c>
+      <c r="G6" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="6">
-        <v>100.33</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.4339</v>
-      </c>
-      <c r="E8" s="6">
-        <v>143.86</v>
-      </c>
-      <c r="F8" s="6">
-        <v>151.89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="9">
-        <v>100.33</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9">
-        <v>143.86</v>
-      </c>
-      <c r="F9" s="9">
-        <v>151.89</v>
+      <c r="H6">
+        <v>1.72</v>
+      </c>
+      <c r="I6" s="1">
+        <v>63.49</v>
+      </c>
+      <c r="J6">
+        <v>1.77</v>
+      </c>
+      <c r="K6" s="1">
+        <v>65.33</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="6">
+        <v>240.25</v>
+      </c>
+      <c r="C11" s="6">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.5708</v>
+      </c>
+      <c r="E11" s="6">
+        <v>377.38</v>
+      </c>
+      <c r="F11" s="6">
+        <v>394.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="9">
+        <v>240.25</v>
+      </c>
+      <c r="C12" s="9">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="9">
+        <v>377.38</v>
+      </c>
+      <c r="F12" s="9">
+        <v>394.27</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
@@ -148,7 +148,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -863,7 +863,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="7">
-        <v>1.5708</v>
+        <v>1.57078</v>
       </c>
       <c r="E11" s="6">
         <v>377.38</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="43">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -539,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -552,13 +555,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -601,230 +604,248 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <v>61.51</v>
       </c>
       <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2">
+        <v>1.399</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="J2">
+        <v>87.89779</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="L2" s="1">
+        <v>92.8801</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>25</v>
       </c>
-      <c r="H2">
-        <v>1.43</v>
-      </c>
-      <c r="I2" s="1">
-        <v>87.95999999999999</v>
-      </c>
-      <c r="J2">
-        <v>1.51</v>
-      </c>
-      <c r="K2" s="1">
-        <v>92.88</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="F3">
+        <v>38.822</v>
+      </c>
+      <c r="G3" t="s">
         <v>26</v>
       </c>
-      <c r="M2">
+      <c r="H3">
+        <v>1.406</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.436</v>
+      </c>
+      <c r="J3">
+        <v>55.748392</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L3" s="1">
+        <v>59.00944</v>
+      </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>31</v>
+      <c r="O3" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>36.333</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4">
+        <v>1.528</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.558</v>
+      </c>
+      <c r="J4">
+        <v>56.606814</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L4" s="1">
+        <v>61.03944</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5">
+        <v>66.684</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5">
+        <v>1.674</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.704</v>
+      </c>
+      <c r="J5">
+        <v>113.629536</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="L5" s="1">
+        <v>116.03016</v>
+      </c>
+      <c r="M5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="F3">
-        <v>38.82</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="E6" t="s">
         <v>25</v>
-      </c>
-      <c r="H3">
-        <v>1.44</v>
-      </c>
-      <c r="I3" s="1">
-        <v>55.9</v>
-      </c>
-      <c r="J3">
-        <v>1.52</v>
-      </c>
-      <c r="K3" s="1">
-        <v>59.01</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4">
-        <v>36.33</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4">
-        <v>1.56</v>
-      </c>
-      <c r="I4" s="1">
-        <v>56.67</v>
-      </c>
-      <c r="J4">
-        <v>1.68</v>
-      </c>
-      <c r="K4" s="1">
-        <v>61.03</v>
-      </c>
-      <c r="L4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5">
-        <v>66.68000000000001</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5">
-        <v>1.7</v>
-      </c>
-      <c r="I5" s="1">
-        <v>113.36</v>
-      </c>
-      <c r="J5">
-        <v>1.74</v>
-      </c>
-      <c r="K5" s="1">
-        <v>116.02</v>
-      </c>
-      <c r="L5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
       </c>
       <c r="F6">
         <v>36.91</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6">
-        <v>1.72</v>
+        <v>1.689</v>
       </c>
       <c r="I6" s="1">
-        <v>63.49</v>
+        <v>1.719</v>
       </c>
       <c r="J6">
+        <v>63.44829</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.77</v>
       </c>
-      <c r="K6" s="1">
-        <v>65.33</v>
-      </c>
-      <c r="L6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>65.33069999999999</v>
+      </c>
+      <c r="M6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>35</v>
+      <c r="O6" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -832,62 +853,62 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="6">
-        <v>240.25</v>
+        <v>240.259</v>
       </c>
       <c r="C11" s="6">
         <v>5</v>
       </c>
       <c r="D11" s="7">
-        <v>1.57078</v>
+        <v>1.570517</v>
       </c>
       <c r="E11" s="6">
-        <v>377.38</v>
+        <v>377.33</v>
       </c>
       <c r="F11" s="6">
-        <v>394.27</v>
+        <v>394.29</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="9">
-        <v>240.25</v>
+        <v>240.259</v>
       </c>
       <c r="C12" s="9">
         <v>5</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="9">
-        <v>377.38</v>
+        <v>377.33</v>
       </c>
       <c r="F12" s="9">
-        <v>394.27</v>
+        <v>394.29</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КИРОВ ТУР ООД/КИРОВ ТУР ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -150,8 +147,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -244,10 +241,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -555,13 +552,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -604,248 +601,230 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>61.51</v>
       </c>
       <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>1.429</v>
+      </c>
+      <c r="I2" s="1">
+        <v>87.898</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>92.88</v>
+      </c>
+      <c r="L2" t="s">
         <v>26</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.429</v>
-      </c>
-      <c r="J2">
-        <v>87.89779</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>92.8801</v>
-      </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
         <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
       </c>
       <c r="F3">
         <v>38.822</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I3" s="1">
-        <v>1.436</v>
+        <v>55.748</v>
       </c>
       <c r="J3">
-        <v>55.748392</v>
+        <v>1.52</v>
       </c>
       <c r="K3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L3" s="1">
-        <v>59.00944</v>
-      </c>
-      <c r="M3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3">
+        <v>59.009</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
         <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
       </c>
       <c r="F4">
         <v>36.333</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>1.528</v>
+        <v>1.558</v>
       </c>
       <c r="I4" s="1">
-        <v>1.558</v>
+        <v>56.607</v>
       </c>
       <c r="J4">
-        <v>56.606814</v>
+        <v>1.68</v>
       </c>
       <c r="K4" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L4" s="1">
-        <v>61.03944</v>
-      </c>
-      <c r="M4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4">
+        <v>61.039</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <v>66.684</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I5" s="1">
-        <v>1.704</v>
+        <v>113.63</v>
       </c>
       <c r="J5">
-        <v>113.629536</v>
+        <v>1.74</v>
       </c>
       <c r="K5" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L5" s="1">
-        <v>116.03016</v>
-      </c>
-      <c r="M5" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5">
+        <v>116.03</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
         <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
       </c>
       <c r="F6">
         <v>36.91</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I6" s="1">
-        <v>1.719</v>
+        <v>63.448</v>
       </c>
       <c r="J6">
-        <v>63.44829</v>
+        <v>1.77</v>
       </c>
       <c r="K6" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L6" s="1">
-        <v>65.33069999999999</v>
-      </c>
-      <c r="M6" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6">
+        <v>65.331</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
+      <c r="N6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -853,49 +832,49 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="6">
         <v>240.259</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>5</v>
       </c>
       <c r="D11" s="7">
-        <v>1.570517</v>
-      </c>
-      <c r="E11" s="6">
-        <v>377.33</v>
-      </c>
-      <c r="F11" s="6">
-        <v>394.29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>1.571</v>
+      </c>
+      <c r="E11" s="7">
+        <v>377.331</v>
+      </c>
+      <c r="F11" s="7">
+        <v>394.289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="9">
         <v>240.259</v>
@@ -905,10 +884,10 @@
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="9">
-        <v>377.33</v>
+        <v>377.331</v>
       </c>
       <c r="F12" s="9">
-        <v>394.29</v>
+        <v>394.289</v>
       </c>
     </row>
   </sheetData>
